--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yan/RustroverProjects/neural-network/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80A310A-98DC-B942-91D8-88FA9EEB57F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FD9E46-23F3-2645-BD38-5F261B845191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="600" windowWidth="37080" windowHeight="21000" xr2:uid="{AB9AD2BD-67DD-D048-AA8F-96EB0BFFEE0C}"/>
   </bookViews>
@@ -16,10 +16,10 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$A$1</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$B$2:$B$6</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$D$45:$D$50</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$E$45:$E$50</definedName>
+    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$D$45:$D$50</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$E$45:$E$50</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,30 +42,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>k</t>
+  </si>
+  <si>
+    <t>Manhattan</t>
+  </si>
+  <si>
+    <t>Euclidean</t>
+  </si>
+  <si>
+    <t>Tief (ReLU)</t>
+  </si>
+  <si>
+    <t>Tief (Tanh)</t>
+  </si>
+  <si>
+    <t>Flach (ReLU)</t>
+  </si>
+  <si>
+    <t>Flach (Tanh)</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>activation_function</t>
+  </si>
+  <si>
+    <t>architecture</t>
   </si>
   <si>
     <t>accuracy</t>
   </si>
   <si>
-    <t>^Manhattan</t>
+    <t>time</t>
   </si>
   <si>
-    <t>^Euclidean</t>
+    <t>ReLU</t>
+  </si>
+  <si>
+    <t>784-10</t>
+  </si>
+  <si>
+    <t>26.596154791s</t>
+  </si>
+  <si>
+    <t>784-64-16-10</t>
+  </si>
+  <si>
+    <t>202.197098041s</t>
+  </si>
+  <si>
+    <t>784-256-128-64-10</t>
+  </si>
+  <si>
+    <t>921.108504459s</t>
+  </si>
+  <si>
+    <t>Tanh</t>
+  </si>
+  <si>
+    <t>27.889009166s</t>
+  </si>
+  <si>
+    <t>194.826271s</t>
+  </si>
+  <si>
+    <t>924.598951167s</t>
+  </si>
+  <si>
+    <t>size</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -89,9 +164,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -144,8 +223,13 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>K-Accuracy-Diagram (euclidean)</a:t>
+              <a:t>Genauigkeit</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> in Abhängigkeit von k</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -189,11 +273,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
+              <c:f>Sheet1!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>accuracy</c:v>
+                  <c:v>Manhattan</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -224,7 +308,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$6</c:f>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -248,24 +332,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$6</c:f>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.96909999999999996</c:v>
+                  <c:v>0.96309999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97140000000000004</c:v>
+                  <c:v>0.96419999999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.96909999999999996</c:v>
+                  <c:v>0.96299999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.96919999999999995</c:v>
+                  <c:v>0.96160000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96350000000000002</c:v>
+                  <c:v>0.95820000000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -273,7 +357,100 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CE2A-AB40-BEFA-079B4A8D9647}"/>
+              <c16:uniqueId val="{00000000-9617-8147-A93F-A113A5E3B8A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Euclidean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.96909999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97140000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.96909999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96919999999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96350000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9617-8147-A93F-A113A5E3B8A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -285,11 +462,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="422845887"/>
-        <c:axId val="422840063"/>
+        <c:axId val="2076593215"/>
+        <c:axId val="2076602175"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="422845887"/>
+        <c:axId val="2076593215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -346,12 +523,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="422840063"/>
+        <c:crossAx val="2076602175"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="422840063"/>
+        <c:axId val="2076602175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -408,7 +585,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="422845887"/>
+        <c:crossAx val="2076593215"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -420,6 +597,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -477,27 +685,13 @@
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buClrTx/>
-              <a:buSzTx/>
-              <a:buFontTx/>
-              <a:buNone/>
-              <a:tabLst/>
+            <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:sysClr>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -505,15 +699,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>K-Accuracy-Diagram (manhattan)</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Genauigkeit von verschiedenen ANNs</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -530,27 +717,13 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
+          <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:sysClr>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -564,99 +737,149 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>Sheet1!$B$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>accuracy</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$14:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Tief (ReLU)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tief (Tanh)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Flach (ReLU)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Flach (Tanh)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:f>Sheet1!$B$14:$B$17</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.99299999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>0.995</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0%">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D81-1246-A75C-0648E9CB5FCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Test</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$14:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Tief (ReLU)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tief (Tanh)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Flach (ReLU)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Flach (Tanh)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:f>Sheet1!$C$14:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.96309999999999996</c:v>
+                  <c:v>0.97699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.96419999999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.96299999999999997</c:v>
+                  <c:v>0.97499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0%">
+                  <c:v>0.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.96160000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.95820000000000005</c:v>
+                  <c:v>0.94499999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D7E9-D244-96BD-90471AF2D2A5}"/>
+              <c16:uniqueId val="{00000001-3D81-1246-A75C-0648E9CB5FCE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -668,13 +891,364 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="465585919"/>
-        <c:axId val="169709951"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="465585919"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2077515199"/>
+        <c:axId val="2077507583"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2077515199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2077507583"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2077507583"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2077515199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:bubbleChart>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$45:$D$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>26.596154791</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202.197098041</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>921.10850445899996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.889009166000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>194.82627099999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>924.598951167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$45:$E$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.91769999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97060000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97409999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91839999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96540000000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97540000000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:bubbleSize>
+            <c:numRef>
+              <c:f>Sheet1!$F$45:$F$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7840</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51360</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>242304</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7840</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51360</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>242304</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:bubbleSize>
+          <c:bubble3D val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1F7B-2C48-A9B8-A64C08D92970}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:bubbleScale val="70"/>
+        <c:showNegBubbles val="0"/>
+        <c:axId val="53006720"/>
+        <c:axId val="53007616"/>
+      </c:bubbleChart>
+      <c:valAx>
+        <c:axId val="53006720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -729,14 +1303,15 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="169709951"/>
+        <c:crossAx val="53007616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="169709951"/>
+        <c:axId val="53007616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -791,7 +1366,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465585919"/>
+        <c:crossAx val="53006720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -806,6 +1381,13 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -920,6 +1502,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1437,7 +2059,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1464,8 +2086,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1566,7 +2188,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1598,6 +2220,528 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="269">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -1956,23 +3100,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>728134</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>97366</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>577850</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>321734</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>198966</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB74FC0-0940-E0BB-1268-593A25191141}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF402484-DEEF-0B6F-A445-A07EE31D1215}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1992,23 +3136,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>97366</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>774700</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>198966</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A329D9B-FF02-4786-A3B0-464E05657F81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B431DE7-52D4-119B-4E85-13DF033D2CEF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2021,6 +3165,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>474133</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>67733</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD0F2880-07FE-A831-4145-0E96DE61A23E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2346,99 +3526,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CF5960-BECB-914F-9109-D06C3BCC6FB3}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>0.96309999999999996</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="C2" s="1">
         <v>0.96909999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3" s="1">
         <v>0.96419999999999995</v>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="C3" s="1">
         <v>0.97140000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>0.96299999999999997</v>
       </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" s="1">
         <v>0.96909999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>7</v>
       </c>
       <c r="B5" s="1">
         <v>0.96160000000000001</v>
       </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="C5" s="1">
         <v>0.96919999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>15</v>
       </c>
       <c r="B6" s="1">
         <v>0.95820000000000005</v>
       </c>
-      <c r="D6">
+      <c r="C6" s="1">
+        <v>0.96350000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.97699999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.995</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.94499999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0.91769999999999996</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1">
-        <v>0.96350000000000002</v>
+      <c r="F35">
+        <v>7840</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0.97060000000000002</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36">
+        <v>51360</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.97409999999999997</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37">
+        <v>242304</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="5">
+        <v>0.91839999999999999</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0.96540000000000004</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39">
+        <v>51360</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="5">
+        <v>0.97540000000000004</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40">
+        <v>242304</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D45" s="4">
+        <v>26.596154791</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.91769999999999996</v>
+      </c>
+      <c r="F45">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D46" s="4">
+        <v>202.197098041</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0.97060000000000002</v>
+      </c>
+      <c r="F46">
+        <v>51360</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D47" s="4">
+        <v>921.10850445899996</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0.97409999999999997</v>
+      </c>
+      <c r="F47">
+        <v>242304</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D48" s="4">
+        <v>27.889009166000001</v>
+      </c>
+      <c r="E48" s="5">
+        <v>0.91839999999999999</v>
+      </c>
+      <c r="F48">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="49" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D49" s="4">
+        <v>194.82627099999999</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0.96540000000000004</v>
+      </c>
+      <c r="F49">
+        <v>51360</v>
+      </c>
+    </row>
+    <row r="50" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D50" s="4">
+        <v>924.598951167</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.97540000000000004</v>
+      </c>
+      <c r="F50">
+        <v>242304</v>
       </c>
     </row>
   </sheetData>
